--- a/artfynd/A 36636-2023 artfynd.xlsx
+++ b/artfynd/A 36636-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123557684</v>
       </c>
       <c r="B2" t="n">
-        <v>90984</v>
+        <v>91001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123557695</v>
+        <v>123557784</v>
       </c>
       <c r="B3" t="n">
-        <v>78775</v>
+        <v>57503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650272</v>
+        <v>650305</v>
       </c>
       <c r="R3" t="n">
-        <v>7162961</v>
+        <v>7162746</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökshack på grov gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +887,7 @@
         <v>123557709</v>
       </c>
       <c r="B4" t="n">
-        <v>91533</v>
+        <v>91550</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123557784</v>
+        <v>123557695</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
+        <v>78781</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650305</v>
+        <v>650272</v>
       </c>
       <c r="R5" t="n">
-        <v>7162746</v>
+        <v>7162961</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,17 +1056,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Födosökshack på grov gran</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36636-2023 artfynd.xlsx
+++ b/artfynd/A 36636-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123557684</v>
+        <v>123557709</v>
       </c>
       <c r="B2" t="n">
-        <v>91001</v>
+        <v>91555</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650242</v>
+        <v>650311</v>
       </c>
       <c r="R2" t="n">
-        <v>7162964</v>
+        <v>7162931</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123557784</v>
+        <v>123557684</v>
       </c>
       <c r="B3" t="n">
-        <v>57503</v>
+        <v>91006</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650305</v>
+        <v>650242</v>
       </c>
       <c r="R3" t="n">
-        <v>7162746</v>
+        <v>7162964</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,17 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosökshack på grov gran</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123557709</v>
+        <v>123557695</v>
       </c>
       <c r="B4" t="n">
-        <v>91550</v>
+        <v>78786</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650311</v>
+        <v>650272</v>
       </c>
       <c r="R4" t="n">
-        <v>7162931</v>
+        <v>7162961</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123557695</v>
+        <v>123557784</v>
       </c>
       <c r="B5" t="n">
-        <v>78781</v>
+        <v>57506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650272</v>
+        <v>650305</v>
       </c>
       <c r="R5" t="n">
-        <v>7162961</v>
+        <v>7162746</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1056,12 +1051,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födosökshack på grov gran</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36636-2023 artfynd.xlsx
+++ b/artfynd/A 36636-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123557709</v>
+        <v>123557684</v>
       </c>
       <c r="B2" t="n">
-        <v>91555</v>
+        <v>91008</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>760</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>650311</v>
+        <v>650242</v>
       </c>
       <c r="R2" t="n">
-        <v>7162931</v>
+        <v>7162964</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123557684</v>
+        <v>123557709</v>
       </c>
       <c r="B3" t="n">
-        <v>91006</v>
+        <v>91557</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>650242</v>
+        <v>650311</v>
       </c>
       <c r="R3" t="n">
-        <v>7162964</v>
+        <v>7162931</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123557695</v>
+        <v>123557784</v>
       </c>
       <c r="B4" t="n">
-        <v>78786</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>650272</v>
+        <v>650305</v>
       </c>
       <c r="R4" t="n">
-        <v>7162961</v>
+        <v>7162746</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +949,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosökshack på grov gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123557784</v>
+        <v>123557695</v>
       </c>
       <c r="B5" t="n">
-        <v>57506</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>650305</v>
+        <v>650272</v>
       </c>
       <c r="R5" t="n">
-        <v>7162746</v>
+        <v>7162961</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,17 +1056,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Födosökshack på grov gran</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
